--- a/assessment_forms/021_europassport_eligibility_assessment--assessment_forms.xlsx
+++ b/assessment_forms/021_europassport_eligibility_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1121,12 +1121,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'irish'}</t>
+          <t>irish</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Irish'}</t>
+          <t>Irish</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'british'}</t>
+          <t>british</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'British'}</t>
+          <t>British</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'german'}</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'German'}</t>
+          <t>German</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'value':_'italian'}</t>
+          <t>italian</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'value': 'Italian'}</t>
+          <t>Italian</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'value':_'portuguese'}</t>
+          <t>portuguese</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'value': 'Portuguese'}</t>
+          <t>Portuguese</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'value':_'dutch'}</t>
+          <t>dutch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'value': 'Dutch'}</t>
+          <t>Dutch</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'value':_'belgian'}</t>
+          <t>belgian</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'value': 'Belgian'}</t>
+          <t>Belgian</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'value':_'swedish'}</t>
+          <t>swedish</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'value': 'Swedish'}</t>
+          <t>Swedish</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_11,_'value':_'danish'}</t>
+          <t>danish</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 11, 'value': 'Danish'}</t>
+          <t>Danish</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_12,_'value':_'norwegian'}</t>
+          <t>norwegian</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 12, 'value': 'Norwegian'}</t>
+          <t>Norwegian</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_13,_'value':_'finnish'}</t>
+          <t>finnish</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 13, 'value': 'Finnish'}</t>
+          <t>Finnish</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_14,_'value':_'greek'}</t>
+          <t>greek</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 14, 'value': 'Greek'}</t>
+          <t>Greek</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_15,_'value':_'cypriot'}</t>
+          <t>cypriot</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 15, 'value': 'Cypriot'}</t>
+          <t>Cypriot</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_16,_'value':_'maltese'}</t>
+          <t>maltese</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 16, 'value': 'Maltese'}</t>
+          <t>Maltese</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_17,_'value':_'cypriot_(dual)'}</t>
+          <t>cypriot_(dual)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 17, 'value': 'Cypriot (Dual)'}</t>
+          <t>Cypriot (Dual)</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_18,_'value':_'british_overseas'}</t>
+          <t>british_overseas</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 18, 'value': 'British Overseas'}</t>
+          <t>British Overseas</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_19,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 19, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_20,_'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 20, 'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'full'}</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Full'}</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'biometric'}</t>
+          <t>biometric</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Biometric'}</t>
+          <t>Biometric</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'biometric_(with_residence_permit)'}</t>
+          <t>biometric_(with_residence_permit)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Biometric (with residence permit)'}</t>
+          <t>Biometric (with residence permit)</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'ireland'}</t>
+          <t>ireland</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Ireland'}</t>
+          <t>Ireland</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'united_kingdom'}</t>
+          <t>united_kingdom</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'United Kingdom'}</t>
+          <t>United Kingdom</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'france'}</t>
+          <t>france</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'France'}</t>
+          <t>France</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'germany'}</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Germany'}</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'spain'}</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Spain'}</t>
+          <t>Spain</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_6,_'value':_'italy'}</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 6, 'value': 'Italy'}</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_7,_'value':_'portugal'}</t>
+          <t>portugal</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 7, 'value': 'Portugal'}</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_8,_'value':_'netherlands'}</t>
+          <t>netherlands</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 8, 'value': 'Netherlands'}</t>
+          <t>Netherlands</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_9,_'value':_'belgium'}</t>
+          <t>belgium</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 9, 'value': 'Belgium'}</t>
+          <t>Belgium</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_10,_'value':_'sweden'}</t>
+          <t>sweden</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 10, 'value': 'Sweden'}</t>
+          <t>Sweden</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_11,_'value':_'denmark'}</t>
+          <t>denmark</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 11, 'value': 'Denmark'}</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_12,_'value':_'norway'}</t>
+          <t>norway</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 12, 'value': 'Norway'}</t>
+          <t>Norway</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_13,_'value':_'finland'}</t>
+          <t>finland</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 13, 'value': 'Finland'}</t>
+          <t>Finland</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_14,_'value':_'greece'}</t>
+          <t>greece</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 14, 'value': 'Greece'}</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_15,_'value':_'cyprus'}</t>
+          <t>cyprus</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 15, 'value': 'Cyprus'}</t>
+          <t>Cyprus</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_16,_'value':_'malta'}</t>
+          <t>malta</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 16, 'value': 'Malta'}</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
@@ -1851,29 +1851,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_17,_'value':_'united_kingdom'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 17, 'value': 'United Kingdom'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>eu_country_choices</t>
+          <t>review_and_follow_up_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_18,_'value':_'other'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 18, 'value': 'Other'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1902,29 +1902,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_false}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': False}</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>review_and_follow_up_choices</t>
+          <t>follow_up_method_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'not_applicable'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Not applicable'}</t>
+          <t>Phone Call</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'phone_call'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Phone Call'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'email'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Email'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1970,29 +1970,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'other'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'value':_'other_(please_specify)'}</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
